--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2020_los_rios.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2020_los_rios.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:14</t>
+    <t xml:space="preserve">2026-09-24 01:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -681,13 +681,13 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="9">
@@ -704,13 +704,13 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="10">
@@ -730,7 +730,7 @@
         <v>-0.12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.49</v>
@@ -753,10 +753,10 @@
         <v>0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="12">
@@ -799,10 +799,10 @@
         <v>-0.2</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="14">
@@ -822,7 +822,7 @@
         <v>0.18</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.51</v>
@@ -845,7 +845,7 @@
         <v>-0.1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.3</v>
